--- a/Role & Permission/Permission.xlsx
+++ b/Role & Permission/Permission.xlsx
@@ -84,9 +84,6 @@
     <t>Can't change admin info</t>
   </si>
   <si>
-    <t>Can't access Test section</t>
-  </si>
-  <si>
     <t>Can't access AccountTest</t>
   </si>
   <si>
@@ -96,9 +93,6 @@
     <t>Invoice manage</t>
   </si>
   <si>
-    <t>Order manage</t>
-  </si>
-  <si>
     <t>Account</t>
   </si>
   <si>
@@ -115,6 +109,12 @@
   </si>
   <si>
     <t>File tab</t>
+  </si>
+  <si>
+    <t>Order history</t>
+  </si>
+  <si>
+    <t>Can't access 'main' section</t>
   </si>
 </sst>
 </file>
@@ -204,7 +204,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -321,11 +321,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -346,13 +366,75 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -364,21 +446,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -388,35 +455,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,57 +762,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="28"/>
-      <c r="B1" s="30"/>
-      <c r="C1" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="17"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="13" t="s">
+      <c r="A1" s="29"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="34"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="24"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="11"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="29"/>
-      <c r="B2" s="27"/>
+      <c r="A2" s="30"/>
+      <c r="B2" s="14"/>
       <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="31"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="31"/>
+      <c r="J2" s="16"/>
       <c r="K2" s="3" t="s">
         <v>14</v>
       </c>
@@ -781,47 +822,47 @@
       <c r="M2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="31"/>
+      <c r="N2" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="16"/>
       <c r="P2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="25"/>
+      <c r="S2" s="12"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="10" t="s">
-        <v>23</v>
+      <c r="B3" s="11"/>
+      <c r="C3" s="31" t="s">
+        <v>22</v>
       </c>
       <c r="D3" s="5"/>
-      <c r="E3" s="31"/>
+      <c r="E3" s="16"/>
       <c r="F3" s="5"/>
       <c r="G3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
-      <c r="J3" s="31"/>
+      <c r="J3" s="16"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="31"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="22"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="25"/>
+      <c r="S3" s="12"/>
       <c r="U3" s="1" t="s">
         <v>4</v>
       </c>
@@ -836,26 +877,26 @@
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="11"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="32"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="31"/>
+      <c r="E4" s="16"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="31"/>
+      <c r="J4" s="16"/>
       <c r="K4" s="5"/>
       <c r="L4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="31"/>
+        <v>21</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="22"/>
       <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="26"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="13"/>
       <c r="U4" s="9"/>
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
@@ -864,123 +905,124 @@
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="31"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="31"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="31"/>
+      <c r="J5" s="16"/>
       <c r="K5" s="5"/>
       <c r="L5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="31"/>
+        <v>31</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="22"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="25"/>
+      <c r="S5" s="12"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="31"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="31"/>
+      <c r="E6" s="16"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="31"/>
+      <c r="J6" s="16"/>
       <c r="K6" s="5"/>
       <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="31"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="22"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="25"/>
+      <c r="S6" s="12"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="31"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="31"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="6"/>
-      <c r="J7" s="31"/>
+      <c r="J7" s="16"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="31"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="22"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
-      <c r="S7" s="25"/>
+      <c r="S7" s="12"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="31"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="34"/>
+      <c r="E8" s="19"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
-      <c r="J8" s="31"/>
+      <c r="J8" s="16"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="31"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="22"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
-      <c r="S8" s="25"/>
+      <c r="S8" s="12"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="27"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="N3:N8"/>
     <mergeCell ref="P1:R1"/>
     <mergeCell ref="P9:R9"/>
     <mergeCell ref="A1:A2"/>
